--- a/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_uva_test_gpu.xlsx
+++ b/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_uva_test_gpu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\dcl3nd\dev\TRITON-SWMM_toolkit\test_data\norfolk_coastal_flooding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDD1BC4-26A2-4D5A-82E7-60712843CB3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A04AED4-55EF-4BFF-BE5E-4925170A333F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="15">
   <si>
     <t>hardware_utilization_strategy</t>
   </si>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t>mem_gb_per_cpu</t>
-  </si>
-  <si>
-    <t>gpu-a6000</t>
   </si>
   <si>
     <t>Use</t>
@@ -713,7 +710,7 @@
         <v>10</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -739,7 +736,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I2" s="11">
         <v>8</v>
@@ -784,7 +781,7 @@
         <v>5</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I3" s="11">
         <v>8</v>
@@ -829,7 +826,7 @@
         <v>6</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I4" s="11">
         <v>8</v>
@@ -874,7 +871,7 @@
         <v>7</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I5" s="11">
         <v>8</v>
@@ -919,7 +916,7 @@
         <v>8</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I6" s="11">
         <v>8</v>
@@ -964,7 +961,7 @@
         <v>16</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I7" s="11">
         <v>8</v>

--- a/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_uva_test_gpu.xlsx
+++ b/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_uva_test_gpu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\dcl3nd\dev\TRITON-SWMM_toolkit\test_data\norfolk_coastal_flooding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A04AED4-55EF-4BFF-BE5E-4925170A333F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B463C042-9BC9-4E5C-B5C3-045FE75CCF2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="15">
   <si>
     <t>hardware_utilization_strategy</t>
   </si>
@@ -343,10 +343,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M7" totalsRowShown="0">
-  <autoFilter ref="A1:M7" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M7">
-    <sortCondition ref="M1:M7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M8" totalsRowShown="0">
+  <autoFilter ref="A1:M8" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M8">
+    <sortCondition ref="M1:M8"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="hardware_utilization_strategy"/>
@@ -655,7 +655,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.85546875" style="14" bestFit="1" customWidth="1"/>
@@ -772,13 +772,13 @@
         <v>1</v>
       </c>
       <c r="E3" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F3" s="10">
         <v>1</v>
       </c>
       <c r="G3" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>12</v>
@@ -788,15 +788,15 @@
       </c>
       <c r="J3" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K3" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L3" s="13">
         <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M3" t="b">
         <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
@@ -817,13 +817,13 @@
         <v>1</v>
       </c>
       <c r="E4" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" s="10">
         <v>1</v>
       </c>
       <c r="G4" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>12</v>
@@ -833,15 +833,15 @@
       </c>
       <c r="J4" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K4" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L4" s="13">
         <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M4" t="b">
         <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
@@ -862,13 +862,13 @@
         <v>1</v>
       </c>
       <c r="E5" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" s="10">
         <v>1</v>
       </c>
       <c r="G5" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>12</v>
@@ -878,15 +878,15 @@
       </c>
       <c r="J5" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K5" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L5" s="13">
         <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M5" t="b">
         <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
@@ -907,13 +907,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" s="10">
         <v>1</v>
       </c>
       <c r="G6" s="10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>12</v>
@@ -923,15 +923,15 @@
       </c>
       <c r="J6" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K6" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L6" s="13">
         <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M6" t="b">
         <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
@@ -949,16 +949,16 @@
         <v>12</v>
       </c>
       <c r="D7" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F7" s="10">
         <v>1</v>
       </c>
       <c r="G7" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>12</v>
@@ -968,17 +968,62 @@
       </c>
       <c r="J7" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K7" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L7" s="13">
         <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
         <v>8</v>
       </c>
       <c r="M7" t="b">
+        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="10">
+        <v>2</v>
+      </c>
+      <c r="E8" s="10">
+        <v>16</v>
+      </c>
+      <c r="F8" s="10">
+        <v>1</v>
+      </c>
+      <c r="G8" s="10">
+        <v>16</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="11">
+        <v>8</v>
+      </c>
+      <c r="J8" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v>16</v>
+      </c>
+      <c r="K8" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v>16</v>
+      </c>
+      <c r="L8" s="13">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>8</v>
+      </c>
+      <c r="M8" t="b">
         <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
         <v>1</v>
       </c>

--- a/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_uva_test_gpu.xlsx
+++ b/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_uva_test_gpu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\dcl3nd\dev\TRITON-SWMM_toolkit\test_data\norfolk_coastal_flooding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B463C042-9BC9-4E5C-B5C3-045FE75CCF2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31BBECF4-A6AD-43F1-9B4E-8CD32042767C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2580" yWindow="2550" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
   <si>
     <t>hardware_utilization_strategy</t>
   </si>
@@ -343,10 +343,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M8" totalsRowShown="0">
-  <autoFilter ref="A1:M8" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M8">
-    <sortCondition ref="M1:M8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M4" totalsRowShown="0">
+  <autoFilter ref="A1:M4" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M4">
+    <sortCondition ref="M1:M4"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="hardware_utilization_strategy"/>
@@ -655,7 +655,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.85546875" style="14" bestFit="1" customWidth="1"/>
@@ -848,186 +848,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="10">
-        <v>1</v>
-      </c>
-      <c r="E5" s="10">
-        <v>6</v>
-      </c>
-      <c r="F5" s="10">
-        <v>1</v>
-      </c>
-      <c r="G5" s="10">
-        <v>6</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="11">
-        <v>8</v>
-      </c>
-      <c r="J5" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>6</v>
-      </c>
-      <c r="K5" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>6</v>
-      </c>
-      <c r="L5" s="13">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>6</v>
-      </c>
-      <c r="M5" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="10">
-        <v>1</v>
-      </c>
-      <c r="E6" s="10">
-        <v>7</v>
-      </c>
-      <c r="F6" s="10">
-        <v>1</v>
-      </c>
-      <c r="G6" s="10">
-        <v>7</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="11">
-        <v>8</v>
-      </c>
-      <c r="J6" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>7</v>
-      </c>
-      <c r="K6" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>7</v>
-      </c>
-      <c r="L6" s="13">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>7</v>
-      </c>
-      <c r="M6" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="10">
-        <v>1</v>
-      </c>
-      <c r="E7" s="10">
-        <v>8</v>
-      </c>
-      <c r="F7" s="10">
-        <v>1</v>
-      </c>
-      <c r="G7" s="10">
-        <v>8</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="11">
-        <v>8</v>
-      </c>
-      <c r="J7" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>8</v>
-      </c>
-      <c r="K7" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>8</v>
-      </c>
-      <c r="L7" s="13">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>8</v>
-      </c>
-      <c r="M7" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="10">
-        <v>2</v>
-      </c>
-      <c r="E8" s="10">
-        <v>16</v>
-      </c>
-      <c r="F8" s="10">
-        <v>1</v>
-      </c>
-      <c r="G8" s="10">
-        <v>16</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="11">
-        <v>8</v>
-      </c>
-      <c r="J8" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>16</v>
-      </c>
-      <c r="K8" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>16</v>
-      </c>
-      <c r="L8" s="13">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>8</v>
-      </c>
-      <c r="M8" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_uva_test_gpu.xlsx
+++ b/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_uva_test_gpu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\dcl3nd\dev\TRITON-SWMM_toolkit\test_data\norfolk_coastal_flooding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31BBECF4-A6AD-43F1-9B4E-8CD32042767C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{71339603-BCB1-42FF-8601-E4EED22A167E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2580" yWindow="2550" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="15">
   <si>
     <t>hardware_utilization_strategy</t>
   </si>
@@ -343,10 +343,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M4" totalsRowShown="0">
-  <autoFilter ref="A1:M4" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M4">
-    <sortCondition ref="M1:M4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M8" totalsRowShown="0">
+  <autoFilter ref="A1:M8" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M8">
+    <sortCondition ref="M1:M8"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="hardware_utilization_strategy"/>
@@ -655,7 +655,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.85546875" style="14" bestFit="1" customWidth="1"/>
@@ -848,6 +848,186 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="10">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10">
+        <v>6</v>
+      </c>
+      <c r="F5" s="10">
+        <v>1</v>
+      </c>
+      <c r="G5" s="10">
+        <v>6</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="11">
+        <v>8</v>
+      </c>
+      <c r="J5" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v>6</v>
+      </c>
+      <c r="K5" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v>6</v>
+      </c>
+      <c r="L5" s="13">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>6</v>
+      </c>
+      <c r="M5" t="b">
+        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="10">
+        <v>1</v>
+      </c>
+      <c r="E6" s="10">
+        <v>7</v>
+      </c>
+      <c r="F6" s="10">
+        <v>1</v>
+      </c>
+      <c r="G6" s="10">
+        <v>7</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="11">
+        <v>8</v>
+      </c>
+      <c r="J6" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v>7</v>
+      </c>
+      <c r="K6" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v>7</v>
+      </c>
+      <c r="L6" s="13">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>7</v>
+      </c>
+      <c r="M6" t="b">
+        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="10">
+        <v>1</v>
+      </c>
+      <c r="E7" s="10">
+        <v>8</v>
+      </c>
+      <c r="F7" s="10">
+        <v>1</v>
+      </c>
+      <c r="G7" s="10">
+        <v>8</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="11">
+        <v>8</v>
+      </c>
+      <c r="J7" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v>8</v>
+      </c>
+      <c r="K7" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v>8</v>
+      </c>
+      <c r="L7" s="13">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>8</v>
+      </c>
+      <c r="M7" t="b">
+        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="10">
+        <v>2</v>
+      </c>
+      <c r="E8" s="10">
+        <v>16</v>
+      </c>
+      <c r="F8" s="10">
+        <v>1</v>
+      </c>
+      <c r="G8" s="10">
+        <v>16</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="11">
+        <v>8</v>
+      </c>
+      <c r="J8" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v>16</v>
+      </c>
+      <c r="K8" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v>16</v>
+      </c>
+      <c r="L8" s="13">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>8</v>
+      </c>
+      <c r="M8" t="b">
+        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_uva_test_gpu.xlsx
+++ b/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_uva_test_gpu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\dcl3nd\dev\TRITON-SWMM_toolkit\test_data\norfolk_coastal_flooding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71339603-BCB1-42FF-8601-E4EED22A167E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB5F63B-1FFA-415E-AFAF-ACF7D8F44D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="2550" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="15">
   <si>
     <t>hardware_utilization_strategy</t>
   </si>
@@ -118,7 +118,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -140,8 +140,14 @@
         <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -229,11 +235,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC6C6C6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC6C6C6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -281,6 +326,30 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -343,10 +412,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M8" totalsRowShown="0">
-  <autoFilter ref="A1:M8" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M8">
-    <sortCondition ref="M1:M8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M7" totalsRowShown="0">
+  <autoFilter ref="A1:M7" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M6">
+    <sortCondition ref="M1:M6"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="hardware_utilization_strategy"/>
@@ -655,7 +724,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.85546875" style="14" bestFit="1" customWidth="1"/>
@@ -862,13 +931,13 @@
         <v>1</v>
       </c>
       <c r="E5" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" s="10">
         <v>1</v>
       </c>
       <c r="G5" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>12</v>
@@ -878,15 +947,15 @@
       </c>
       <c r="J5" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K5" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L5" s="13">
         <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M5" t="b">
         <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
@@ -904,16 +973,16 @@
         <v>12</v>
       </c>
       <c r="D6" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F6" s="10">
         <v>1</v>
       </c>
       <c r="G6" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>12</v>
@@ -923,107 +992,62 @@
       </c>
       <c r="J6" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K6" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L6" s="13">
         <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M6" t="b">
         <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="10">
-        <v>1</v>
-      </c>
-      <c r="E7" s="10">
-        <v>8</v>
-      </c>
-      <c r="F7" s="10">
-        <v>1</v>
-      </c>
-      <c r="G7" s="10">
-        <v>8</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="11">
-        <v>8</v>
-      </c>
-      <c r="J7" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>8</v>
-      </c>
-      <c r="K7" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>8</v>
-      </c>
-      <c r="L7" s="13">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>8</v>
-      </c>
-      <c r="M7" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="10">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="20">
         <v>2</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E7" s="20">
         <v>16</v>
       </c>
-      <c r="F8" s="10">
-        <v>1</v>
-      </c>
-      <c r="G8" s="10">
+      <c r="F7" s="20">
+        <v>1</v>
+      </c>
+      <c r="G7" s="20">
         <v>16</v>
       </c>
-      <c r="H8" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="11">
-        <v>8</v>
-      </c>
-      <c r="J8" s="12">
+      <c r="H7" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="22">
+        <v>8</v>
+      </c>
+      <c r="J7" s="23">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
         <v>16</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K7" s="23">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
         <v>16</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L7" s="24">
         <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
         <v>8</v>
       </c>
-      <c r="M8" t="b">
+      <c r="M7" t="b">
         <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
         <v>1</v>
       </c>

--- a/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_uva_test_gpu.xlsx
+++ b/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_uva_test_gpu.xlsx
@@ -1,126 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\dcl3nd\dev\TRITON-SWMM_toolkit\test_data\norfolk_coastal_flooding\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB5F63B-1FFA-415E-AFAF-ACF7D8F44D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="15">
-  <si>
-    <t>hardware_utilization_strategy</t>
-  </si>
-  <si>
-    <t>device</t>
-  </si>
-  <si>
-    <t>run_mode</t>
-  </si>
-  <si>
-    <t>n_nodes</t>
-  </si>
-  <si>
-    <t>n_mpi_procs</t>
-  </si>
-  <si>
-    <t>n_omp_threads</t>
-  </si>
-  <si>
-    <t>n_gpus</t>
-  </si>
-  <si>
-    <t>hpc_ensemble_partition</t>
-  </si>
-  <si>
-    <t>total_OpenMP_threads</t>
-  </si>
-  <si>
-    <t>total_devices</t>
-  </si>
-  <si>
-    <t>devices_per_node</t>
-  </si>
-  <si>
-    <t>GPU</t>
-  </si>
-  <si>
-    <t>gpu</t>
-  </si>
-  <si>
-    <t>mem_gb_per_cpu</t>
-  </si>
-  <si>
-    <t>Use</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="6">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -279,77 +211,77 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="25">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -359,20 +291,16 @@
   <dxfs count="1">
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
+        <condense val="0"/>
+        <color rgb="FF3F3F76"/>
+        <extend val="0"/>
+        <sz val="11"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF3F3F76"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -380,8 +308,8 @@
           <bgColor rgb="FFFFCC99"/>
         </patternFill>
       </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="left" vertical="bottom"/>
+      <border>
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
@@ -400,37 +328,97 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M7" totalsRowShown="0">
-  <autoFilter ref="A1:M7" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M7" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A1:M7"/>
+  <sortState ref="A2:M6">
     <sortCondition ref="M1:M6"/>
   </sortState>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="hardware_utilization_strategy"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="device"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="run_mode"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="n_nodes"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="n_mpi_procs"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="n_omp_threads"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="n_gpus"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="hpc_ensemble_partition"/>
-    <tableColumn id="9" xr3:uid="{26339B98-C3B5-4C3B-9409-F4B744B2B94C}" name="mem_gb_per_cpu" dataDxfId="0"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="total_OpenMP_threads"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="total_devices"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="devices_per_node"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Use"/>
+    <tableColumn id="1" name="hardware_utilization_strategy"/>
+    <tableColumn id="2" name="device"/>
+    <tableColumn id="3" name="run_mode"/>
+    <tableColumn id="4" name="n_nodes"/>
+    <tableColumn id="5" name="n_mpi_procs"/>
+    <tableColumn id="6" name="n_omp_threads"/>
+    <tableColumn id="7" name="n_gpus"/>
+    <tableColumn id="8" name="hpc_ensemble_partition"/>
+    <tableColumn id="9" name="mem_gb_per_cpu" dataDxfId="0"/>
+    <tableColumn id="10" name="total_OpenMP_threads"/>
+    <tableColumn id="11" name="total_devices"/>
+    <tableColumn id="12" name="devices_per_node"/>
+    <tableColumn id="13" name="Use"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -720,342 +708,440 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29.85546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.42578125" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="28.28515625" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.28515625" customWidth="1"/>
-    <col min="10" max="10" width="24.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19" style="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.85546875" style="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col width="29.85546875" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="9.28515625" bestFit="1" customWidth="1" style="14" min="2" max="2"/>
+    <col width="9.28515625" bestFit="1" customWidth="1" style="15" min="3" max="3"/>
+    <col width="19" bestFit="1" customWidth="1" style="16" min="4" max="4"/>
+    <col width="22.42578125" bestFit="1" customWidth="1" style="16" min="5" max="5"/>
+    <col width="28.28515625" bestFit="1" customWidth="1" style="16" min="6" max="7"/>
+    <col width="28.28515625" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="28.28515625" customWidth="1" min="9" max="9"/>
+    <col width="24.7109375" bestFit="1" customWidth="1" style="16" min="10" max="10"/>
+    <col width="19" bestFit="1" customWidth="1" style="16" min="11" max="11"/>
+    <col width="19.85546875" bestFit="1" customWidth="1" style="16" min="12" max="12"/>
+    <col width="13.5703125" bestFit="1" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>sa_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>hardware_utilization_strategy</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>device</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>run_mode</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>n_nodes</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>n_mpi_procs</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>n_omp_threads</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>n_gpus</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>hpc_ensemble_partition</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>mem_gb_per_cpu</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>total_OpenMP_threads</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>total_devices</t>
+        </is>
+      </c>
+      <c r="M1" s="6" t="inlineStr">
+        <is>
+          <t>devices_per_node</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customHeight="1">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>gpu</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>gpu</t>
+        </is>
+      </c>
+      <c r="J2" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K2" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v/>
+      </c>
+      <c r="L2" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v/>
+      </c>
+      <c r="M2" s="13">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v/>
+      </c>
+      <c r="N2">
+        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>gpu</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>gpu</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v/>
+      </c>
+      <c r="L3" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v/>
+      </c>
+      <c r="M3" s="13">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v/>
+      </c>
+      <c r="N3">
+        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>gpu</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>gpu</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v/>
+      </c>
+      <c r="L4" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v/>
+      </c>
+      <c r="M4" s="13">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v/>
+      </c>
+      <c r="N4">
+        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>gpu</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>gpu</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v/>
+      </c>
+      <c r="L5" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v/>
+      </c>
+      <c r="M5" s="13">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v/>
+      </c>
+      <c r="N5">
+        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customHeight="1">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>gpu</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>gpu</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v/>
+      </c>
+      <c r="L6" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v/>
+      </c>
+      <c r="M6" s="13">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v/>
+      </c>
+      <c r="N6">
+        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="5" t="s">
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>gpu</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="G7" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>gpu</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="10">
-        <v>1</v>
-      </c>
-      <c r="E2" s="10">
-        <v>1</v>
-      </c>
-      <c r="F2" s="10">
-        <v>1</v>
-      </c>
-      <c r="G2" s="10">
-        <v>1</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="11">
-        <v>8</v>
-      </c>
-      <c r="J2" s="12">
+      <c r="K7" s="23">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>1</v>
-      </c>
-      <c r="K2" s="12">
+        <v/>
+      </c>
+      <c r="L7" s="23">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>1</v>
-      </c>
-      <c r="L2" s="13">
+        <v/>
+      </c>
+      <c r="M7" s="24">
         <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-      <c r="M2" t="b">
+        <v/>
+      </c>
+      <c r="N7">
         <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="10">
-        <v>1</v>
-      </c>
-      <c r="E3" s="10">
-        <v>2</v>
-      </c>
-      <c r="F3" s="10">
-        <v>1</v>
-      </c>
-      <c r="G3" s="10">
-        <v>2</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="11">
-        <v>8</v>
-      </c>
-      <c r="J3" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>2</v>
-      </c>
-      <c r="K3" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>2</v>
-      </c>
-      <c r="L3" s="13">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>2</v>
-      </c>
-      <c r="M3" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="10">
-        <v>1</v>
-      </c>
-      <c r="E4" s="10">
-        <v>5</v>
-      </c>
-      <c r="F4" s="10">
-        <v>1</v>
-      </c>
-      <c r="G4" s="10">
-        <v>5</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="11">
-        <v>8</v>
-      </c>
-      <c r="J4" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>5</v>
-      </c>
-      <c r="K4" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>5</v>
-      </c>
-      <c r="L4" s="13">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>5</v>
-      </c>
-      <c r="M4" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="10">
-        <v>1</v>
-      </c>
-      <c r="E5" s="10">
-        <v>8</v>
-      </c>
-      <c r="F5" s="10">
-        <v>1</v>
-      </c>
-      <c r="G5" s="10">
-        <v>8</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="11">
-        <v>8</v>
-      </c>
-      <c r="J5" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>8</v>
-      </c>
-      <c r="K5" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>8</v>
-      </c>
-      <c r="L5" s="13">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>8</v>
-      </c>
-      <c r="M5" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="10">
-        <v>2</v>
-      </c>
-      <c r="E6" s="10">
-        <v>10</v>
-      </c>
-      <c r="F6" s="10">
-        <v>1</v>
-      </c>
-      <c r="G6" s="10">
-        <v>10</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="11">
-        <v>8</v>
-      </c>
-      <c r="J6" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>10</v>
-      </c>
-      <c r="K6" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>10</v>
-      </c>
-      <c r="L6" s="13">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>5</v>
-      </c>
-      <c r="M6" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="20">
-        <v>2</v>
-      </c>
-      <c r="E7" s="20">
-        <v>16</v>
-      </c>
-      <c r="F7" s="20">
-        <v>1</v>
-      </c>
-      <c r="G7" s="20">
-        <v>16</v>
-      </c>
-      <c r="H7" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="22">
-        <v>8</v>
-      </c>
-      <c r="J7" s="23">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>16</v>
-      </c>
-      <c r="K7" s="23">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>16</v>
-      </c>
-      <c r="L7" s="24">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>8</v>
-      </c>
-      <c r="M7" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
+        <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>